--- a/db/A7XLK-1302-Parking.xlsx
+++ b/db/A7XLK-1302-Parking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F87937-144A-F744-B91A-1B98DEF0FAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79494ED6-E229-5540-B5FA-13C18F1855FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17460" yWindow="4160" windowWidth="28260" windowHeight="17320" xr2:uid="{67953B6A-770D-0343-84EB-D1DF795C4940}"/>
+    <workbookView xWindow="3220" yWindow="12940" windowWidth="28260" windowHeight="17320" xr2:uid="{67953B6A-770D-0343-84EB-D1DF795C4940}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -48,10 +48,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>遠雄新未來</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>皇翔</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -69,6 +65,10 @@
   </si>
   <si>
     <t>合計</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遠雄</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -453,12 +453,12 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>1272</v>
@@ -473,7 +473,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>1780</v>
@@ -488,7 +488,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>514</v>
@@ -503,7 +503,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>897</v>
@@ -518,7 +518,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <f>SUM(B3:B6)</f>
